--- a/hpfc_2024/outputs/019f9e14-2737-7782-aa21-8e5d0a37d66e/hpfc_2024_inspection.xlsx
+++ b/hpfc_2024/outputs/019f9e14-2737-7782-aa21-8e5d0a37d66e/hpfc_2024_inspection.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R4dbb408318c142e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="2" r:id="R68b6c87137604f63"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="3" r:id="Ree05def447304190"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calibration" sheetId="4" r:id="R0e7a91accf954185"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliation" sheetId="5" r:id="Rdcdfca0d468148eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly" sheetId="6" r:id="R9c12b6bf65fc4a22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rf5aaf55d013d4461"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="2" r:id="R2b3cec228eb34a38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="3" r:id="Rc29ab7c01b4447ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calibration" sheetId="4" r:id="Rb750582747644ded"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliation" sheetId="5" r:id="R88af3fe84b0e4945"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly" sheetId="6" r:id="Rf09945df2f9a4c0c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -15,8 +15,8 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:authors>
-    <x:author>tc={613B1846-A5B2-8E16-6BD7-BDA690DED8E4}</x:author>
-    <x:author>tc={71C5FCE1-075C-D566-67BC-BA6C97B6F6DD}</x:author>
+    <x:author>tc={C09B0CC0-43D7-8A73-FB10-0F2BB555BD1B}</x:author>
+    <x:author>tc={27D12593-3FBF-4592-D2DB-C98CE50B9466}</x:author>
   </x:authors>
   <x:commentList>
     <x:comment ref="B4" authorId="0">
@@ -740,7 +740,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re16d2d495dcb444c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7b6c99469d5d45a8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -770,7 +770,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5f05cbf9c5a94679"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf8219d591afb43e2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -781,7 +781,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:person displayName="Codex" id="{A5B7D027-7706-4A6A-8FB9-83F22750FC09}"/>
+  <xltc:person displayName="Codex" id="{B994829E-BA18-4B60-ADF5-07A5D4F6D0A4}"/>
 </xltc:personList>
 </file>
 
@@ -1035,10 +1035,10 @@
 
 <file path=xl/threadedcomments/threadedcomment.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:ThreadedComments xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:threadedComment ref="B4" dT="2026-07-26T12:58:39.568" personId="{A5B7D027-7706-4A6A-8FB9-83F22750FC09}" id="{613B1846-A5B2-8E16-6BD7-BDA690DED8E4}">
+  <xltc:threadedComment ref="B4" dT="2026-07-26T13:19:52.418" personId="{B994829E-BA18-4B60-ADF5-07A5D4F6D0A4}" id="{C09B0CC0-43D7-8A73-FB10-0F2BB555BD1B}">
     <xltc:text>Exact neutrality tolerance for the selected M01–M03 and Q2–Q4 calibration products.</xltc:text>
   </xltc:threadedComment>
-  <xltc:threadedComment ref="B6" dT="2026-07-26T12:58:39.569" personId="{A5B7D027-7706-4A6A-8FB9-83F22750FC09}" id="{71C5FCE1-075C-D566-67BC-BA6C97B6F6DD}">
+  <xltc:threadedComment ref="B6" dT="2026-07-26T13:19:52.419" personId="{B994829E-BA18-4B60-ADF5-07A5D4F6D0A4}" id="{27D12593-3FBF-4592-D2DB-C98CE50B9466}">
     <xltc:text>Synthetic teaching convention: market_activity above this threshold is considered usable.</xltc:text>
   </xltc:threadedComment>
 </xltc:ThreadedComments>
@@ -1062,7 +1062,7 @@
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
       <x:c r="A1" s="34" t="str">
-        <x:v>HTW Summer School — value-neutral 2024 HPFC</x:v>
+        <x:v>HTW Summer School — arbitrage-consistent 2024 HPFC</x:v>
       </x:c>
       <x:c r="B1" s="34"/>
       <x:c r="C1" s="34"/>
@@ -1511,7 +1511,7 @@
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="66" t="str">
-        <x:v>The HPFC is neutral to the selected Base and Peak futures. CAL and Q1 are cross-checks; their sub-cent residuals arise only from quote rounding. M04–M12 are deliberately illiquid and are not calibration inputs.</x:v>
+        <x:v>The HPFC is contract-consistent with the selected Base and Peak futures. CAL and Q1 are cross-checks; their sub-cent residuals arise only from quote rounding. M04–M12 are deliberately illiquid and are not calibration inputs. Value-neutrality belongs to the subsequent hedge constraint.</x:v>
       </x:c>
       <x:c r="B42" s="67"/>
       <x:c r="C42" s="67"/>
@@ -1557,7 +1557,7 @@
     <x:mergeCell ref="A42:J44"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60348734cded47b4"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22d6a28bbf3e47c2"/>
 </x:worksheet>
 </file>
 
@@ -1684,7 +1684,7 @@
     <x:mergeCell ref="A1:B1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R75b09cecad514524"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22fead0b96fe4944"/>
 </x:worksheet>
 </file>
 
@@ -1911,7 +1911,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd86eef7c20b14936"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8585568372424861"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2193,7 +2193,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77e81103aca34034"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R849659b5124d4ea3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3205,7 +3205,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d18f062418f4d1e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R161577c885904bab"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3365,7 +3365,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e034c257e49448a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67b70a4435d34ab7"/>
   </x:tableParts>
 </x:worksheet>
 </file>